--- a/plantillas/21.xlsx
+++ b/plantillas/21.xlsx
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/21.xlsx
+++ b/plantillas/21.xlsx
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/21.xlsx
+++ b/plantillas/21.xlsx
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
